--- a/output/北塩原村_国予算R7R8_MECE.xlsx
+++ b/output/北塩原村_国予算R7R8_MECE.xlsx
@@ -9,12 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_結論" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_原典の記述" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_レビューとの食い違い" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_MECEチェック" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_正本に入れる" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_正本に入れる文章" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_照会" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_原典" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01b_令和6・7年度の原典" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_レビューとの食い違い" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_当方の誤りと訂正" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_年度の経過" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_MECEチェック" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_正本に入れる" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_正本に入れる文章" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_照会" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_原典" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -158,6 +161,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -530,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -576,7 +588,7 @@
     <row r="8" ht="62" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>4. 二つめ。強度行動障害の中核的人材の養成は令和8年度に新規化したものではない。令和7年度予算にも同じ名称・同額（21百万円）の事業があり、「令和9年度から全国の都道府県で養成が開始できるよう」という記述も令和7年度からある。広域的支援人材の配置も令和7年度から同額（4.3億円）である。令和8年度で変わったのは項目の立て方であり、政策の新設ではない。</t>
+          <t>4. 二つめ。強度行動障害の中核的人材の養成は、政策として令和8年度に始まったものではない。21百万円の中核的人材養成研修事業は【令和6年度補正予算】として令和7年度の資料に載っており、「令和9年度から全国の都道府県で養成が開始できるよう」という記述もその補正予算の説明の中にある。広域的支援人材の配置は令和6年度当初予算で「新たに配置」とされたものである（4.3億円。令和5年度は3.9億円）。ただし令和8年度の資料は中核的人材の養成に【新規】と明記している。当初予算としては新規であり、政策としては令和6年度補正予算から先行実施されている。この二つを分けて書いた（04シート）。</t>
         </is>
       </c>
     </row>
@@ -615,19 +627,285 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>10. 令和8年10月11日。反証確認（訂正版）と令和6年度の原典を受けて当方の指摘②を再点検したところ、当方の側にも誤りがあった（03シート）。「令和7年度予算にも21百万円がある」と書いたが、令和7年度の資料に載っているのは【令和6年度補正予算】としての21百万円であり、令和7年度の当初予算ではない。前年度補正を当年度の予算として扱う誤りで、当方が指摘①でレビューに指摘したものと同じ種類である。「広域的支援人材も令和7年度から」も1年遅く、令和6年度当初予算からである。「政策の新設ではない」も、原典の【新規】表示を消しており、当初予算上の新規と政策としての新設を分けるべきであった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>11. 同じ誤りを繰り返さないため、自己点検を直した。従来は「補正予算の見出しの後ろに並んでいるか」を令和8年度の資料にしか当てていなかった。令和7年度の資料にも当て、広域的支援人材が令和6年度の原典に「新たに配置」とあること、令和8年度の原典に【新規】の表示があることも生成のたびに確かめる。年度の経過は04シートに、原典のあるものとレビューの記述にとどまるものを分けて並べた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>12. 反証確認は、高次脳機能障害者支援法が令和8年4月1日に施行されたことを厚生労働省の法令・施行通知で確認できるとする。しかし当該の法令・通知そのものは添付されておらず、当方は取得できない。施行日は計画本文に書かない（ＹＳ-8は体系だけを書いている）。原典を頂ければ照合して反映する。強度行動障害の平成25・26年度の研修、高次脳機能障害の平成13〜17年度のモデル事業及び平成18年度の支援普及事業も同様に原典がないため、04シートで「レビューの記述（当方は未確認）」と分けた。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A16:C16"/>
     <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A15:C15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="84" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>村への照会</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>build_kitashiobara_shoukai_bun.py がここから読み込む。県への確認は既に起票したＭ-99に寄せる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>番号</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>宛先</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>件名</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Ｍ-105</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>村</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>国は、市町村内における家庭・教育・福祉の連携を進めるため、教育委員会、福祉部局、学校、障害児通所支援事業所等の関係者が協議を行う場の設置と、連携の役割を担う「地域連携推進マネジャー」の配置を行う事業を設けています（地域生活支援事業等の内数）。実施主体は市町村です。次をご教示ください。①本村においてこの事業を実施する意向の有無。②教育と福祉の連携の調整を担う部署又は職（保健福祉課、こども家庭センター、教育委員会、相談支援事業所のいずれか、又はその他）。③既に設けている協議の場（インクルージョン推進のための協議の場、医療的ケア児等支援の協議の場、自立支援協議会）で代えられるかどうか。専任の職を新たに置くことを求めるものではありません。誰が調整するかが決まっていないと、計画に書いた連携が動かないためです。</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>令和８年11月28日（金）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>原典（手元にあるもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>予算資料は3件とも現物がある。本書の国の施策に関する記述は、レビューの記述ではなくこの原典を出所とする。令和6年度の資料は、年度の起点を確かめるために令和8年10月11日に受領したものである。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>資料名</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>頁数</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ファイル</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>リポジトリ内の場所</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>令和8年度 障害保健福祉部予算案の概要</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>001744478.pdf</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>source/国資料/令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>令和7年度 障害保健福祉部予算案の概要</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>001512596.pdf</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>source/国資料/令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>障害保健福祉関係主管課長会議資料（令和6年3月）。令和6年度障害保健福祉関係予算案を含む</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>001231504.pdf</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>source/国資料/令和6年度障害保健福祉関係予算案_主管課長会議資料_001231504.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>レビューが挙げた追加確認資料（厚生労働省の各ページ）は、当方の環境からは取得できない（組織のネットワーク方針により接続が403で遮断される）。また、そのURLの一覧には、中核的人材養成研修事業と自立支援医療等のオンライン化に同じURLが当てられており、令和8年度予算案の概要として添付と異なる番号が挙げられている。本書はこれらを用いず、添付された予算資料3件のみを出所としている。高次脳機能障害者支援法の施行日についても、反証確認は厚生労働省の法令・施行通知で確認できるとするが、当該の法令・通知そのものは添付されておらず当方は取得できない。原典を頂ければ照合し、計画本文に反映する。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1037,7 +1315,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>追記（ＹＳ-3）。令和7年度と同額であり、新設ではない</t>
+          <t>追記（ＹＳ-3）。令和6年度当初予算で「新たに配置」とされたもので、令和7年度・令和8年度は同額の継続である（04シート）</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1342,7 @@
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>追記（ＹＳ-3）。令和9年度は本計画の初年度に当たる</t>
+          <t>追記（ＹＳ-3）。令和9年度は本計画の初年度に当たる。原典の【新規】は当初予算としての新規であり、政策は令和6年度補正予算から先行している（04シート）</t>
         </is>
       </c>
     </row>
@@ -1240,6 +1518,238 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>令和6年度・令和7年度の原典から拾った記述（現物と照合済み）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>年度の起点を確かめるために読んだもの。令和8年度の資料だけでは「いつ始まったか」が決まらない。前年度額の括弧書きと【○年度補正予算】の見出しを遡って見る。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>資料</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>頁</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>原典の記述</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>本書での扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>強度行動障害　広域的支援人材の新たな配置</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>強度行動障害を有する者に対する地域支援機能の強化 4.3億円（3.9億円）。著しい行動障害が生じているなどの難しい事案に対応する現場の職員を支援するため、高い専門性を有する「広域的支援人材」を発達障害者支援センター等に新たに配置し、現場に訪問等をして適切なアセスメントを行う</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>広域的支援人材は令和6年度当初予算からである。当方が「令和7年度から」と書いていたのを訂正した（03シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>強度行動障害　前年度額</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>令和5年度は3.9億円。事業そのものは令和6年度より前からある</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>04シートの令和5年度の行の根拠</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>p.10</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>補正</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>強度行動障害　中核的人材養成研修事業</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>【令和6年度補正予算】強度行動障害者支援のための中核的人材養成研修事業 21百万円。強度行動障害者支援について専門性の高い中核的人材を養成するとともに、令和9年度から全国の都道府県で中核的人材養成が開始できるよう、研修指導者の養成及び研修指導者が活用する教材の開発等を実施する</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>21百万円は令和6年度補正予算の枠である。当方が「令和7年度予算にもある」と書いていたのを訂正した（03シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>p.10</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>強度行動障害　令和7年度当初の立て方</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>① 広域的支援人材の配置及び集中的支援の実施、支援のネットワークの構築等の推進 4.3億円（4.3億円）。② 強度行動障害者支援のための中核的人材養成（金額の記載なし）</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>令和7年度の当初予算には②に金額が付いていない。金額は【令和6年度補正予算】の側にある</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>p.8</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>高次脳機能障害　令和7年度の立て方</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>高次脳機能障害及びその関連障害に対する地域支援ネットワーク構築の促進 1.3億円（1.3億円）。協力医療機関（医療機関、リハビリ機関等）及び専門支援機関（就労支援機関、教育機関等）を確保・明確化し、地域支援ネットワークを構築する</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の「支援センター・コーディネーター・地域協議会・専門的な医療機関・当事者及び家族の相互支援」との違いを原典で確かめた。前年度額は1.3億円で令和6年度も同額である</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1315,7 +1825,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>中核的人材の養成を令和8年度の新規施策としている</t>
+          <t>中核的人材の養成を政策として令和8年度の新設としている</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -1325,12 +1835,12 @@
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>令和7年度予算にも「強度行動障害者支援のための中核的人材養成研修事業21百万円」があり（R7 p.10）、「令和9年度から全国の都道府県で中核的人材養成が開始できるよう」という記述も令和7年度からある。広域的支援人材の配置も令和7年度から同額（4.3億円）である</t>
+          <t>21百万円の「強度行動障害者支援のための中核的人材養成研修事業」は、令和7年度の資料では【令和6年度補正予算】の枠に置かれている（R7 p.10）。「令和9年度から全国の都道府県で中核的人材養成が開始できるよう」という記述もその補正予算の説明の中にある。広域的支援人材の配置は令和6年度当初予算で「新たに配置」とされたものである（4.3億円。令和5年度は3.9億円。R6 p.3）。一方、令和8年度の資料は「中核的人材の養成【新規】21百万円」と明記している（R8 p.10）</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>令和8年度で変わったのは項目の立て方であり、政策の新設ではない。本計画には「令和9年度から都道府県で養成が始まる」という事実だけを書く</t>
+          <t>「当初予算としては令和8年度の新規」と「政策としては令和6年度補正予算から先行実施」を分けて書く。本計画には年度の別を持ち込まず、「令和9年度から都道府県で養成が始まる」という事実だけを書く。当方の当初の指摘にも年度の取り違えがあった（03シート）</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1862,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>施行日は書かない。確認できた体系だけを書く（ＹＳ-8）。施行の状況は県に照会する（Ｍ-99に追加）</t>
+          <t>施行日は書かない。確認できた体系だけを書く（ＹＳ-8）。施行の状況は県に照会する（Ｍ-99に追加）。反証確認は施行日を厚生労働省の法令・施行通知で確認できるとするが、当該の法令・通知は添付されておらず当方は取得できない。原典を得るまで本文には書かない（04シート）</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1875,795 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>当方の指摘の誤りと訂正（令和8年10月11日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>反証確認（訂正版）と令和6年度の原典を受けて、当方の指摘②を再点検した結果である。当方がレビューに指摘したのと同じ種類の誤りがあった。正本の本文（ＹＳ-1・ＹＳ-3）は年度を言わずに書いていたため、本文の訂正は要らなかった。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>誤り</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>重さ</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>当方がどう書いていたか</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>原典ではどうか</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>どう直したか</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>前年度補正を当年度の予算として扱った</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>重大</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>当方の指摘②は「令和7年度予算にも『強度行動障害者支援のための中核的人材養成研修事業21百万円』がある」と書いた</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度の資料に載っている21百万円は【令和6年度補正予算】の枠にあり、令和7年度の当初予算ではない（R7 p.10）</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>当方が指摘①でレビューに指摘した誤り（前年度補正を当年度予算として扱う）と同じ種類である。02シートの指摘を書き直し、自己点検に「令和7年度の資料でも補正予算の見出しの後ろに並んでいるか」を加えた</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>事業の開始年度を1年遅く書いた</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>当方の指摘②は「広域的支援人材の配置も令和7年度からある（4.3億円で同額）」と書いた</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>令和6年度当初予算に「高い専門性を有する『広域的支援人材』を発達障害者支援センター等に新たに配置し」とある。予算額は4.3億円で、令和5年度は3.9億円（R6 p.3）。令和6年度からである</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>「令和7年度と同額」という見方だけで年度を決めると、同額が続く事業の開始年度を取り違える。前年度額の括弧書きを遡って確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>【新規】の表示を無いものとして扱った</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>当方の指摘②は「令和8年度で変わったのは項目の立て方であり、政策の新設ではない」と書いた</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度の資料は「② 強度行動障害の状態にある者への支援のための中核的人材の養成【新規】 21百万円」と明記している（R8 p.10）。当初予算としては新規である</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>「当初予算上の新規」と「政策としての新設」を分ける。01シートの区分に加えて、原典の【新規】表示をそのまま記録する</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>同じ誤りを繰り返さないため、自己点検を直した。①「補正予算の見出しの後ろに並んでいるか」を令和7年度の資料にも当てる。②広域的支援人材が令和6年度の原典に「新たに配置」とあることを確かめる。③令和8年度の原典に【新規】の表示があることを確かめる。④訂正前の主張が本書に残っていないこと、訂正後の記述が入っていることを確かめる。いずれも生成のたびに走る。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>強度行動障害・高次脳機能障害の年度の経過</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>原典で確かめたものと、レビューの記述にとどまり当方が確認できていないものを分ける。確認できていないものは計画本文に書かない。高次脳機能障害者支援法の施行日も、法令・通知の現物が無いため本文には書かない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>分野</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>事業名・内容</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>金額</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>原典の新規表記</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>出所の別</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>令和5年度</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>強度行動障害を有する者に対する地域支援機能の強化</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>3.9億円</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R6 p.3の前年度額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>同事業。高い専門性を有する「広域的支援人材」を発達障害者支援センター等に新たに配置</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>4.3億円</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>本文に「新たに配置」</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R6 p.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>補正</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>強度行動障害者支援のための中核的人材養成研修事業。令和9年度から全国の都道府県で中核的人材養成が開始できるよう、研修指導者の養成及び教材の開発等</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>21百万円</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R7 p.10の【令和6年度補正予算】）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>広域的支援人材の配置及び集中的支援の実施、支援のネットワークの構築等の推進</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>4.3億円（4.3億円）</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G9" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R7 p.10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>広域的支援人材の配置及び集中的支援の実施、支援のネットワークの構築等の推進</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>4.3億円（4.3億円）</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R8 p.10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>強度行動障害の状態にある者への支援のための中核的人材の養成。専門研修プログラムを用いて養成し、令和9年度から全国の都道府県で養成が開始できるよう、指導的人材の養成及び教材の開発等</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>21百万円</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>【新規】</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R8 p.10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>全国の都道府県で中核的人材の養成を開始（予定）。本計画の初年度に当たる</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R7 p.10・R8 p.10）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>平成25・26年度</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>強度行動障害支援者養成研修（基礎研修・実践研修）の開始</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>レビューの記述（当方は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>強度行動障害</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>令和4・5年度</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>中核的人材の養成に関する研究及びモデル研修</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>レビューの記述（当方は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>高次脳機能障害及びその関連障害に対する地域支援ネットワーク構築の促進</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>1.3億円</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R7 p.8の前年度額）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>同事業。協力医療機関及び専門支援機関の確保・明確化と、地域支援ネットワークの構築</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1.3億円（1.3億円）</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R7 p.8）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>当初</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>高次脳機能障害者の支援施策の推進。都道府県等における支援センターの設置、支援コーディネーターによる相談支援、地域協議会の設置、専門的な医療機関の確保、当事者・家族の相互支援</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>1.3億円（1.3億円）</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（R8 p.8）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>平成13〜17年度</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>高次脳機能障害支援モデル事業</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>レビューの記述（当方は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>平成18年度</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>高次脳機能障害支援普及事業の開始</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>レビューの記述（当方は未確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>令和8年4月1日</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>高次脳機能障害者支援法の施行</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>レビューの記述（当方は未確認。法令・通知の現物がない）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1432,7 +2730,7 @@
           <t>あり</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1454,7 +2752,7 @@
           <t>正本は令和9年度の改定のみに触れ、令和8年度の改定（決定済み）に触れていない</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-1・ＹＳ-7）。当方の見落としであった。見込量は令和7年度の実績を基礎としているため、単価の改定を織り込まないと給付費を低く見積もる</t>
         </is>
@@ -1476,7 +2774,7 @@
           <t>県のワンストップ窓口・介護テクノロジー・処遇改善加算・経営基盤まであり</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-2）。サポートセンターの正式な位置づけと小規模事業所の協働化を足す</t>
         </is>
@@ -1498,7 +2796,7 @@
           <t>村の手話言語条例はあるが法律が無い</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-1・ＹＳ-6）</t>
         </is>
@@ -1520,7 +2818,7 @@
           <t>正本自身が「正面から対応する基本施策がない」と認識している</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-6）。第5章2（1）住民への情報提供等に置く</t>
         </is>
@@ -1542,7 +2840,7 @@
           <t>詳細にあり</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1564,7 +2862,7 @@
           <t>5機能と実績の記録まであり</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1586,7 +2884,7 @@
           <t>国の新規論点として挙げ、生活介護の内数として人数を見込むのみ</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="D13" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-8）。相談の導線として書く。施行日は書かない</t>
         </is>
@@ -1608,7 +2906,7 @@
           <t>対象者と支援ニーズの把握、行動援護等との接続、圏域での体制はあり。広域的支援人材・中核的人材が無い</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-3）</t>
         </is>
@@ -1630,7 +2928,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-3）</t>
         </is>
@@ -1652,7 +2950,7 @@
           <t>ペアレントトレーニング・ペアレントメンターあり</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1674,7 +2972,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-3）</t>
         </is>
@@ -1696,7 +2994,7 @@
           <t>インクルージョンの協議の場、教育委員会、学校、卒業移行まであり</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-3）。誰が調整を担うかを決める。照会Ｍ-105</t>
         </is>
@@ -1718,7 +3016,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-3）。市町村が実施主体であるため実施の意向を照会</t>
         </is>
@@ -1740,7 +3038,7 @@
           <t>詳細にあり</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1762,7 +3060,7 @@
           <t>第7章1でこころの健康を扱うが、手帳や診断の有無を問わないという書き方になっていない</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-8）に含める</t>
         </is>
@@ -1784,7 +3082,7 @@
           <t>一般就労との連携はあり</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D22" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-5）</t>
         </is>
@@ -1806,7 +3104,7 @@
           <t>優先調達あり</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-5）</t>
         </is>
@@ -1828,7 +3126,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-5）。村で事業を起こすのではなく県の窓口につなぐ</t>
         </is>
@@ -1850,7 +3148,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-5）</t>
         </is>
@@ -1872,7 +3170,7 @@
           <t>詳細にあり</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1894,7 +3192,7 @@
           <t>詳細にあり</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="17" t="inlineStr">
         <is>
           <t>維持</t>
         </is>
@@ -1916,7 +3214,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-4）。令和9年度第4四半期の運用開始想定であり計画期間の途中で動き出す。成果目標にはしない</t>
         </is>
@@ -1938,7 +3236,7 @@
           <t>記述なし</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="D29" s="18" t="inlineStr">
         <is>
           <t>追記（ＹＳ-4）。計画実施状況調査機能の拡充は市町村計画のPDCAに直に関わる</t>
         </is>
@@ -1997,7 +3295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2233,7 +3531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2676,221 +3974,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="84" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>村への照会</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>build_kitashiobara_shoukai_bun.py がここから読み込む。県への確認は既に起票したＭ-99に寄せる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>番号</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>宛先</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>件名</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Ｍ-105</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>村</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>家庭・教育・福祉の連携を進める事業と地域連携推進マネジャー</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>国は、市町村内における家庭・教育・福祉の連携を進めるため、教育委員会、福祉部局、学校、障害児通所支援事業所等の関係者が協議を行う場の設置と、連携の役割を担う「地域連携推進マネジャー」の配置を行う事業を設けています（地域生活支援事業等の内数）。実施主体は市町村です。次をご教示ください。①本村においてこの事業を実施する意向の有無。②教育と福祉の連携の調整を担う部署又は職（保健福祉課、こども家庭センター、教育委員会、相談支援事業所のいずれか、又はその他）。③既に設けている協議の場（インクルージョン推進のための協議の場、医療的ケア児等支援の協議の場、自立支援協議会）で代えられるかどうか。専任の職を新たに置くことを求めるものではありません。誰が調整するかが決まっていないと、計画に書いた連携が動かないためです。</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>令和８年11月28日（金）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="54" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>原典（手元にあるもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>予算資料は2件とも現物がある。本書の国の施策に関する記述は、レビューの記述ではなくこの原典を出所とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>資料名</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>頁数</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ファイル</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>リポジトリ内の場所</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>令和8年度</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>令和8年度 障害保健福祉部予算案の概要</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>001744478.pdf</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>source/国資料/令和8年度障害保健福祉部予算案の概要_001744478.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>令和7年度</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>令和7年度 障害保健福祉部予算案の概要</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>001512596.pdf</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>source/国資料/令和7年度障害保健福祉部予算案の概要_001512596.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>レビューが挙げた追加確認資料（厚生労働省の各ページ）は、当方の環境からは取得できない（組織のネットワーク方針により接続が403で遮断される）。また、そのURLの一覧には、中核的人材養成研修事業と自立支援医療等のオンライン化に同じURLが当てられており、令和8年度予算案の概要として添付と異なる番号が挙げられている。本書はこれらを用いず、添付された予算資料2件のみを出所としている。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/北塩原村_国予算R7R8_MECE.xlsx
+++ b/output/北塩原村_国予算R7R8_MECE.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,12 +644,19 @@
     <row r="16" ht="62" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12. 反証確認は、高次脳機能障害者支援法が令和8年4月1日に施行されたことを厚生労働省の法令・施行通知で確認できるとする。しかし当該の法令・通知そのものは添付されておらず、当方は取得できない。施行日は計画本文に書かない（ＹＳ-8は体系だけを書いている）。原典を頂ければ照合して反映する。強度行動障害の平成25・26年度の研修、高次脳機能障害の平成13〜17年度のモデル事業及び平成18年度の支援普及事業も同様に原典がないため、04シートで「レビューの記述（当方は未確認）」と分けた。</t>
+          <t>12. 強度行動障害の平成25・26年度の研修、高次脳機能障害の平成13〜17年度のモデル事業及び平成18年度の支援普及事業は原典がないため、04シートで「レビューの記述（当方は未確認）」と分けた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="62" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>13. 令和8年10月11日。高次脳機能障害者支援法の施行通知（障精発0415第1号 令和8年4月15日）と施行令（令和8年政令第60号）の原典を得た。法は令和7年12月24日に公布され、令和8年4月1日から施行されている。予算資料を根拠に施行を述べることを退けた判断は変えないが、施行の事実そのものはレビューのとおりであった。誤っていたのは根拠の置き方であって、事実ではない。公布と施行の日は法令・通知を出所として本文に書いた（ＫＮ-1）。本書は予算資料のことだけを扱い、法令のことは build_kitashiobara_kojino.py に置いた。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
@@ -659,6 +666,7 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
@@ -1862,7 +1870,7 @@
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>施行日は書かない。確認できた体系だけを書く（ＹＳ-8）。施行の状況は県に照会する（Ｍ-99に追加）。反証確認は施行日を厚生労働省の法令・施行通知で確認できるとするが、当該の法令・通知は添付されておらず当方は取得できない。原典を得るまで本文には書かない（04シート）</t>
+          <t>予算資料を根拠に施行を述べることは退ける。ＹＳ-8は確認できた体系だけを書いている。施行の状況は県に照会する（Ｍ-99・Ｍ-107）。ただし施行の事実そのものはレビューのとおりであった。令和8年10月11日に施行通知（障精発0415第1号）と施行令（令和8年政令第60号）の原典を得たため、公布と施行の日は法令・通知を出所として本文に書いた（ＫＮ-1。build_kitashiobara_kojino.py）。誤っていたのは根拠の置き方であって、事実ではない</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2625,32 +2633,69 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>令和7年12月24日</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>高次脳機能障害者支援法（令和7年法律第96号）の公布</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（施行通知 障精発0415第1号。令和8年10月11日に受領）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>高次脳機能障害</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
           <t>令和8年4月1日</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>高次脳機能障害者支援法の施行</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>高次脳機能障害者支援法及び施行令（令和8年政令第60号）の施行</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>レビューの記述（当方は未確認。法令・通知の現物がない）</t>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>原典あり（施行通知 障精発0415第1号・施行令附則第1条。令和8年10月11日に受領。予算資料ではない）</t>
         </is>
       </c>
     </row>
